--- a/testFile/case/CompanyExcel.xlsx
+++ b/testFile/case/CompanyExcel.xlsx
@@ -4,19 +4,35 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17475" windowHeight="8062" activeTab="2"/>
+    <workbookView windowWidth="20317" windowHeight="9727" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="company" sheetId="1" r:id="rId1"/>
     <sheet name="notice" sheetId="2" r:id="rId2"/>
     <sheet name="card" sheetId="3" r:id="rId3"/>
+    <sheet name="sitereport" sheetId="4" r:id="rId4"/>
+    <sheet name="dahua" sheetId="5" r:id="rId5"/>
+    <sheet name="exhortation" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="170">
   <si>
     <t>测试用例编号</t>
   </si>
@@ -170,7 +186,8 @@
     <t>{
   "content": "测试",
   "noticeId": "2",
-  "title": "刘珂珂测试"
+  "title": "刘珂珂测试",
+  "type": 0
 }</t>
   </si>
   <si>
@@ -300,6 +317,41 @@
     <t>/buswash/system/notice/search/3</t>
   </si>
   <si>
+    <t>公告模块/专项通知</t>
+  </si>
+  <si>
+    <t>[签到机]专项通知查询</t>
+  </si>
+  <si>
+    <t>/buswash/system/notice/signDevice/search</t>
+  </si>
+  <si>
+    <t>{
+   "Content-Type":"application/json",
+   "token":"10000294_123456"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "jobId": "90179035"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": {
+    "noticeId": "1805146488372879361",
+    "title": "行车提醒",
+    "pushTime": "2024-10-15 13:29:59",
+    "type": 1,
+    "content": "路况复杂，请注意行车安全"
+  },
+  "total": null,
+  "success": true
+}</t>
+  </si>
+  <si>
     <t>公告模块/公告状态</t>
   </si>
   <si>
@@ -378,11 +430,741 @@
   <si>
     <t>"retmsg":"删除失败"</t>
   </si>
+  <si>
+    <t>卡模块/卡导出</t>
+  </si>
+  <si>
+    <t>司机卡-临时卡导出</t>
+  </si>
+  <si>
+    <t>/buswash/card/driver/export</t>
+  </si>
+  <si>
+    <t>{
+  "beginTime": "2023-11-07 23:59:59",
+  "creatorName": "1",
+  "current": 0,
+  "endTime": "2023-11-07 00:00:00",
+  "id": 0,
+  "number": "1",
+  "perSize": 0,
+  "personJobId": "1",
+  "personName": "1",
+  "role": "1",
+  "roleList": [1],
+  "siteId": 0,
+  "state": "1",
+  "status": "1",
+  "type": "1"
+}</t>
+  </si>
+  <si>
+    <t>卡模块/巡更钮导出</t>
+  </si>
+  <si>
+    <t>巡更钮导出</t>
+  </si>
+  <si>
+    <t>/buswash/card/patrolButton/export</t>
+  </si>
+  <si>
+    <t>卡模块/卡查询</t>
+  </si>
+  <si>
+    <t>卡查询</t>
+  </si>
+  <si>
+    <t>/buswash/card/search</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": [],
+  "total": 0,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>卡模块/安保钮导出</t>
+  </si>
+  <si>
+    <t>安保钮导出</t>
+  </si>
+  <si>
+    <t>/buswash/card/securityButton/export</t>
+  </si>
+  <si>
+    <t>卡模块/卡操作</t>
+  </si>
+  <si>
+    <t>卡启用-停用</t>
+  </si>
+  <si>
+    <t>/buswash/card/state</t>
+  </si>
+  <si>
+    <t>{
+  "id": 180617,
+  "state": 2
+}</t>
+  </si>
+  <si>
+    <t>场站报表模块/异常明细</t>
+  </si>
+  <si>
+    <t>司机报到异常明细</t>
+  </si>
+  <si>
+    <t>/buswash/sitereport/abnormal/attend/export</t>
+  </si>
+  <si>
+    <t>{
+  "abnormalList": [11],
+  "dateRange": [
+    "2023-11-07 00:00:00","2023-11-07 23:59:59"
+  ],
+  "orgNum": [1],
+  "siteNum": [1]
+}</t>
+  </si>
+  <si>
+    <t>出场异常明细</t>
+  </si>
+  <si>
+    <t>/buswash/sitereport/abnormal/gate/out/export</t>
+  </si>
+  <si>
+    <t>{
+  "abnormalList": [1],
+  "dateRange": [
+    "2023-11-07 00:00:00","2023-11-07 23:59:59"
+  ],
+  "orgNum": [1],
+  "siteNum": [1]
+}</t>
+  </si>
+  <si>
+    <t>场站报表模块/报表导出</t>
+  </si>
+  <si>
+    <t>异常汇总报表导出</t>
+  </si>
+  <si>
+    <t>/buswash/sitereport/abnormal/report/export</t>
+  </si>
+  <si>
+    <t>{
+  "dateRange": [
+    "2023-11-07 00:00:00","2023-11-07 23:59:59"
+  ],
+  "dateType": "DAY",
+  "orgNum": [1],
+  "siteNum": [1]
+}</t>
+  </si>
+  <si>
+    <t>综合情况统计报表导出</t>
+  </si>
+  <si>
+    <t>/buswash/sitereport/complex/business/export</t>
+  </si>
+  <si>
+    <t>{
+  "dateRange": {
+    "dateEnd": "2023-11-06",
+    "dateStart": "2023-11-06"
+  },
+  "siteIdList": [10]
+}</t>
+  </si>
+  <si>
+    <t>场站报表模块/pdf导出</t>
+  </si>
+  <si>
+    <t>晨会个人台账pdf导出</t>
+  </si>
+  <si>
+    <t>/buswash/sitereport/morningMeeting/personal/ledger</t>
+  </si>
+  <si>
+    <t>{
+  "date": "2023-11-07",
+  "orgNum": "0"
+}</t>
+  </si>
+  <si>
+    <t>大华通道模块/拜访部门</t>
+  </si>
+  <si>
+    <t>拜访部门（大华组织）</t>
+  </si>
+  <si>
+    <t>get</t>
+  </si>
+  <si>
+    <t>/buswash/channel/dahua/card/department</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": {
+    "department": {
+      "id": 1,
+      "name": "根节点",
+      "children": [
+        {
+          "id": 2,
+          "name": "一公司",
+          "children": [
+            {
+              "id": 9,
+              "name": "阮家桥",
+              "children": null
+            }
+          ]
+        },
+        {
+          "id": 4,
+          "name": "三公司",
+          "children": null
+        },
+        {
+          "id": 14,
+          "name": "二修",
+          "children": null
+        },
+        {
+          "id": 3,
+          "name": "二公司",
+          "children": null
+        },
+        {
+          "id": 5,
+          "name": "五公司",
+          "children": [
+            {
+              "id": 10,
+              "name": "九和路",
+              "children": [
+                {
+                  "id": 28,
+                  "name": "中车",
+                  "children": null
+                },
+                {
+                  "id": 29,
+                  "name": "二修",
+                  "children": null
+                },
+                {
+                  "id": 27,
+                  "name": "充电公司",
+                  "children": null
+                },
+                {
+                  "id": 25,
+                  "name": "巴士传媒",
+                  "children": null
+                },
+                {
+                  "id": 33,
+                  "name": "房产经营公司",
+                  "children": null
+                },
+                {
+                  "id": 31,
+                  "name": "自行车公司",
+                  "children": null
+                },
+                {
+                  "id": 30,
+                  "name": "餐饮公司",
+                  "children": null
+                },
+                {
+                  "id": 26,
+                  "name": "驾培",
+                  "children": null
+                }
+              ]
+            }
+          ]
+        },
+        {
+          "id": 6,
+          "name": "六公司",
+          "children": null
+        },
+        {
+          "id": 7,
+          "name": "电车公司",
+          "children": [
+            {
+              "id": 22,
+              "name": "一修",
+              "children": null
+            },
+            {
+              "id": 16,
+              "name": "一公司",
+              "children": null
+            },
+            {
+              "id": 18,
+              "name": "三公司",
+              "children": null
+            },
+            {
+              "id": 23,
+              "name": "三墩场站",
+              "children": null
+            },
+            {
+              "id": 17,
+              "name": "二公司",
+              "children": null
+            },
+            {
+              "id": 19,
+              "name": "五公司",
+              "children": null
+            },
+            {
+              "id": 20,
+              "name": "六公司",
+              "children": null
+            },
+            {
+              "id": 21,
+              "name": "其他",
+              "children": null
+            },
+            {
+              "id": 24,
+              "name": "石塘场站",
+              "children": null
+            }
+          ]
+        },
+        {
+          "id": 12,
+          "name": "金通科技",
+          "children": null
+        }
+      ]
+    }
+  },
+  "total": null,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>大华通道模块/通道查询</t>
+  </si>
+  <si>
+    <t>大华通道查询</t>
+  </si>
+  <si>
+    <t>/buswash/channel/dahua/search</t>
+  </si>
+  <si>
+    <t>{
+  "channelName": "1",
+  "current": 1,
+  "perSize": 1,
+  "siteId": 1
+}</t>
+  </si>
+  <si>
+    <t>大华通道模块/访客导出</t>
+  </si>
+  <si>
+    <t>大华访客导出</t>
+  </si>
+  <si>
+    <t>/buswash/channel/dahua/visitor/export</t>
+  </si>
+  <si>
+    <t>{
+  "actualArriveTime": "2023-11-07",
+  "current": 0,
+  "deptIds": "1",
+  "isvDeptName": "1",
+  "isvName": "测试",
+  "perSize": 0,
+  "planArriveTime": "2023-11-07",
+  "signInCentryBox": "1",
+  "signOutCentryBox": "1",
+  "siteName": "1",
+  "status": "1",
+  "visitorDW": "1",
+  "visitorName": "1",
+  "visitorPhone": "1"
+}</t>
+  </si>
+  <si>
+    <t>大华通道模块/访客查询</t>
+  </si>
+  <si>
+    <t>大华访客查询</t>
+  </si>
+  <si>
+    <t>/buswash/channel/dahua/visitor/search</t>
+  </si>
+  <si>
+    <t>大华门禁模块/设备信息</t>
+  </si>
+  <si>
+    <t>门禁设备信息</t>
+  </si>
+  <si>
+    <t>/buswash/access/control/device/info</t>
+  </si>
+  <si>
+    <t>{
+  "orgCode": "001004"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": [
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000001",
+      "deviceName": "九和路停车场_北门_进口",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000001$7$0$0",
+      "channelName": "九和路停车场_北门_进口"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000002",
+      "deviceName": "九和路停车场_南门_出口_",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000002$7$0$0",
+      "channelName": "九和路停车场_南门_出口_"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000003",
+      "deviceName": "九和路停车场_南门_进口_",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000003$7$0$0",
+      "channelName": "九和路停车场_南门_进口_"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000004",
+      "deviceName": "九和路停车场_北门_出口",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000004$7$0$0",
+      "channelName": "九和路停车场_北门_出口"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000007",
+      "deviceName": "九和路停车场_南门_进口",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000007$7$0$0",
+      "channelName": "九和路停车场_南门_进口"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000008",
+      "deviceName": "九和路停车场_南门_出口",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000008$7$0$0",
+      "channelName": "九和路停车场_南门_出口"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000010",
+      "deviceName": "九和路停车场_北门_进口__",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000010$7$0$0",
+      "channelName": "九和路停车场_北门_进口___通道1"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000011",
+      "deviceName": "九和路停车场_北门_出口_",
+      "deviceModelName": "人脸门禁",
+      "channelCode": "1000011$7$0$0",
+      "channelName": "九和路停车场_北门_出口_"
+    },
+    {
+      "orgCode": "001004",
+      "deviceCode": "1000015",
+      "deviceName": "九和路停车场_广告门_进出口",
+      "deviceModelName": "DH-ASC1201A",
+      "channelCode": "1000015$7$0$0",
+      "channelName": "九和路停车场_广告门_进出口"
+    }
+  ],
+  "total": null,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>大华门禁模块/门禁记录</t>
+  </si>
+  <si>
+    <t>大华门禁记录导出</t>
+  </si>
+  <si>
+    <t>/buswash/access/swing/record/export</t>
+  </si>
+  <si>
+    <t>{
+  "channelCode": "1",
+  "current": 1,
+  "endSwingTime": "2023-12-12 23:59:59",
+  "enterOrExit": 1,
+  "openResult": 1,
+  "openType": 1,
+  "perSize": 1,
+  "personName": "1",
+  "siteId": 1,
+  "startSwingTime": "2023-12-12 00:00:00"
+}</t>
+  </si>
+  <si>
+    <t>大华门禁模块/记录查询</t>
+  </si>
+  <si>
+    <t>刷卡记录查询</t>
+  </si>
+  <si>
+    <t>/buswash/access/swing/record/search</t>
+  </si>
+  <si>
+    <t>岗前叮嘱模块/附件查询</t>
+  </si>
+  <si>
+    <t>屏保图片附件查询</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/attach/path/1</t>
+  </si>
+  <si>
+    <t>岗前叮嘱模块/岗前叮嘱</t>
+  </si>
+  <si>
+    <t>创建-编辑岗前叮嘱</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/cu</t>
+  </si>
+  <si>
+    <t>{
+  "attachName": "",
+  "attachPath": "",
+  "attachPathList": [],
+  "attachType": 0,
+  "id": 1,
+  "jobIdList": [],
+  "orgNum": "35",
+  "richTextContent": "测试文本内容",
+  "siteId": 0,
+  "stayTime": 0,
+  "title": "测试测试",
+  "type": 0
+}</t>
+  </si>
+  <si>
+    <t>岗前叮嘱模块/查询工号</t>
+  </si>
+  <si>
+    <t>岗前叮嘱查询对于工号</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/jobIds/1</t>
+  </si>
+  <si>
+    <t>岗前叮嘱模块/操作日志</t>
+  </si>
+  <si>
+    <t>岗前叮嘱操作日志</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/oper/log</t>
+  </si>
+  <si>
+    <t>{
+  "id": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": [
+    {
+      "id": 30065,
+      "exhortationId": 1,
+      "operName": "管理员",
+      "operId": 28,
+      "operType": 4,
+      "createTime": "2023-10-10 11:19:33",
+      "reviewedTime": null
+    },
+    {
+      "id": 30061,
+      "exhortationId": 1,
+      "operName": "管理员",
+      "operId": 28,
+      "operType": 3,
+      "createTime": "2023-10-10 11:18:38",
+      "reviewedTime": null
+    },
+    {
+      "id": 60029,
+      "exhortationId": 1,
+      "operName": "管理员",
+      "operId": 28,
+      "operType": 4,
+      "createTime": "2023-10-10 10:59:32",
+      "reviewedTime": null
+    },
+    {
+      "id": 39,
+      "exhortationId": 1,
+      "operName": "管理员",
+      "operId": 28,
+      "operType": 3,
+      "createTime": "2023-10-10 10:59:02",
+      "reviewedTime": null
+    },
+    {
+      "id": 29,
+      "exhortationId": 1,
+      "operName": "管理员",
+      "operId": 28,
+      "operType": 4,
+      "createTime": "2023-10-09 18:57:10",
+      "reviewedTime": null
+    }
+  ],
+  "total": null,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>发布岗前叮嘱</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/published</t>
+  </si>
+  <si>
+    <t>{
+  "id": 1,
+  "published": 0
+}</t>
+  </si>
+  <si>
+    <t>审核岗前叮嘱</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/reviewed</t>
+  </si>
+  <si>
+    <t>{
+  "id": 1,
+  "review": 0
+}</t>
+  </si>
+  <si>
+    <t>岗前叮嘱模块/屏保素材</t>
+  </si>
+  <si>
+    <t>签到机查询屏保素材</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/screensaver</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": {
+    "exhortationConfig": null,
+    "attachPathList": null
+  },
+  "total": null,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>岗前叮嘱、屏保查询</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/search</t>
+  </si>
+  <si>
+    <t>{
+  "current": 1,
+  "perSize": 1,
+  "siteIdList": [],
+  "typeList": []
+}</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": [
+    {
+      "id": 1,
+      "siteId": 0,
+      "orgNum": "35",
+      "orgName": null,
+      "title": "测试测试",
+      "operName": "刘珂珂",
+      "stayTime": 0,
+      "type": 0,
+      "reviewed": 1,
+      "published": 0,
+      "attachName": "",
+      "attachPath": "",
+      "attachType": 0,
+      "richTextContent": "测试文本内容",
+      "createTime": "2023-10-08 14:49:58",
+      "updateTime": "2023-12-12 16:45:04",
+      "reviewedTime": null
+    }
+  ],
+  "total": 26,
+  "success": true
+}</t>
+  </si>
+  <si>
+    <t>签到机查询岗前叮嘱</t>
+  </si>
+  <si>
+    <t>/buswash/exhortation/config/station</t>
+  </si>
+  <si>
+    <t>{
+  "retcode": "0",
+  "retmsg": "操作成功",
+  "data": {
+    "stayTime": null,
+    "publicExhortation": null,
+    "personalExhortation": null
+  },
+  "total": null,
+  "success": true
+}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -992,15 +1774,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1499,14 +2278,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.5486725663717" customWidth="1"/>
     <col min="2" max="2" width="27.0176991150442" customWidth="1"/>
     <col min="3" max="3" width="28.8141592920354" customWidth="1"/>
     <col min="4" max="4" width="14.0088495575221" customWidth="1"/>
-    <col min="5" max="5" width="38.3097345132743" customWidth="1"/>
+    <col min="5" max="5" width="41.2212389380531" customWidth="1"/>
     <col min="6" max="6" width="49.1858407079646" customWidth="1"/>
     <col min="7" max="7" width="35.0530973451327" customWidth="1"/>
     <col min="8" max="8" width="15.5309734513274" customWidth="1"/>
@@ -1749,18 +2528,50 @@
         <v>54</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="108" customHeight="1" spans="1:10">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8">
-        <v>200</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="G9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <v>200</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1773,14 +2584,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="15.141592920354" customWidth="1"/>
     <col min="2" max="2" width="26.2920353982301" customWidth="1"/>
     <col min="3" max="3" width="24.7610619469027" customWidth="1"/>
     <col min="4" max="4" width="14.141592920354" customWidth="1"/>
-    <col min="5" max="5" width="35.5840707964602" customWidth="1"/>
+    <col min="5" max="5" width="37.7079646017699" customWidth="1"/>
     <col min="6" max="6" width="46.5929203539823" customWidth="1"/>
     <col min="7" max="7" width="32.2654867256637" customWidth="1"/>
     <col min="8" max="8" width="18.0619469026549" customWidth="1"/>
@@ -1825,31 +2636,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="H2">
         <v>200</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" ht="94.5" spans="1:10">
@@ -1857,31 +2668,964 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
         <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>65</v>
+      <c r="G3" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="H3">
         <v>200</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>66</v>
+      <c r="I3" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="J3" t="s">
-        <v>67</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" ht="168" customHeight="1" spans="1:8">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" ht="149" customHeight="1" spans="1:8">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" ht="130" customHeight="1" spans="1:10">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="151" customHeight="1" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" ht="94.5" spans="1:10">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="15.070796460177" customWidth="1"/>
+    <col min="2" max="2" width="26.353982300885" customWidth="1"/>
+    <col min="3" max="3" width="24.7610619469027" customWidth="1"/>
+    <col min="4" max="4" width="14.4070796460177" customWidth="1"/>
+    <col min="5" max="5" width="51.3097345132743" customWidth="1"/>
+    <col min="6" max="6" width="46.3362831858407" customWidth="1"/>
+    <col min="7" max="7" width="39.7610619469027" customWidth="1"/>
+    <col min="8" max="8" width="15.4070796460177" customWidth="1"/>
+    <col min="9" max="9" width="29.8761061946903" customWidth="1"/>
+    <col min="10" max="10" width="25.5575221238938" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="129" customHeight="1" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" ht="121.5" spans="1:8">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" ht="121.5" spans="1:8">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" ht="94.5" spans="1:8">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" ht="54" spans="1:8">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="13.6814159292035" customWidth="1"/>
+    <col min="2" max="2" width="23.3716814159292" customWidth="1"/>
+    <col min="3" max="3" width="23.6371681415929" customWidth="1"/>
+    <col min="4" max="4" width="12.0265486725664" customWidth="1"/>
+    <col min="5" max="5" width="49.4513274336283" customWidth="1"/>
+    <col min="6" max="6" width="48.1858407079646" customWidth="1"/>
+    <col min="7" max="7" width="34.9203539823009" customWidth="1"/>
+    <col min="8" max="8" width="19.3274336283186" customWidth="1"/>
+    <col min="9" max="9" width="34.3893805309735" customWidth="1"/>
+    <col min="10" max="10" width="21.5132743362832" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="129" customHeight="1" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="94.5" spans="1:10">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="150" customHeight="1" spans="1:8">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" ht="162" customHeight="1" spans="1:10">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="159" customHeight="1" spans="1:10">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="119" customHeight="1" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" ht="141" customHeight="1" spans="1:10">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="13.6814159292035" customWidth="1"/>
+    <col min="2" max="2" width="23.5663716814159" customWidth="1"/>
+    <col min="3" max="3" width="24.9026548672566" customWidth="1"/>
+    <col min="4" max="4" width="11.6902654867257" customWidth="1"/>
+    <col min="5" max="5" width="45.3451327433628" customWidth="1"/>
+    <col min="6" max="6" width="47.9911504424779" customWidth="1"/>
+    <col min="7" max="7" width="30.8053097345133" customWidth="1"/>
+    <col min="8" max="8" width="17.0619469026549" customWidth="1"/>
+    <col min="9" max="9" width="28.6194690265487" customWidth="1"/>
+    <col min="10" max="10" width="22.9734513274336" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="129" customHeight="1" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2">
+        <v>200</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="142" customHeight="1" spans="1:10">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" spans="1:10">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="172" customHeight="1" spans="1:10">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="94.5" spans="1:10">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="94.5" spans="1:10">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="123" customHeight="1" spans="1:10">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1" spans="1:10">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9">
+        <v>200</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="175.5" spans="1:10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
+        <v>200</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
